--- a/medical_surveys_questionnaires/010_medical_procedure_knowledge_quiz--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/010_medical_procedure_knowledge_quiz--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,46 +515,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>medical_procedure_knowledge_quiz</t>
+          <t>medical_procedure_knowledge_quiz_specialty</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Medical Procedures Quiz</t>
+          <t>What is your specialty?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>medical_procedure_knowledge_quiz_procedures</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is your specialty?</t>
+          <t>What medical procedures do you perform most often?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>medical_procedure_knowledge_quiz_license_number</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -584,51 +584,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>medical_procedure_knowledge_quiz_hospital_affiliation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Select medical procedures</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Select all that apply</t>
-        </is>
-      </c>
+          <t>What is your hospital affiliation?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>medical_procedure_knowledge_quiz_note</t>
+          <t>medical_procedure_knowledge_quiz_equipment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Additional comments or notes</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Please add any additional comments or notes</t>
-        </is>
-      </c>
+          <t>What type of medical equipment do you have access to?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -638,40 +630,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>medical_procedure_knowledge_quiz_experience</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>How long have you been working in the medical field?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>medical_procedure_knowledge_quiz_notes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Additional comments or notes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -689,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>What is your phone number?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -712,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>question_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>What is your email?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -730,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>question_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is your medical school?</t>
+          <t>What is your date of birth?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -753,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>question_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What is your hospital affiliation?</t>
+          <t>What is your time of birth?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -776,355 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>question_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What type of medical equipment do you have access to?</t>
+          <t>Question 12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>question_7</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>What is your role?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>question_8</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>How long have you been working in the medical field?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>question_9</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>What medical procedures do you perform most often?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Select all that apply</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>question_10</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Additional comments or notes</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Please add any additional comments or notes</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>question_11</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>question_12</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question_13</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_14</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_15</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What is your medical school?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_16</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is your hospital affiliation?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_17</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What type of medical equipment do you have access to?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_18</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What is your role?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question_19</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>How long have you been working in the medical field?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>question_20</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>What medical procedures do you perform most often?</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Select all that apply</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1141,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1169,952 +827,357 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>medical_procedure_knowledge_quiz_specialty_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option1':_'cardiology'}</t>
+          <t>cardiology</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option1': 'Cardiology'}</t>
+          <t>Cardiology</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>medical_procedure_knowledge_quiz_specialty_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option2':_'dermatology'}</t>
+          <t>dermatology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option2': 'Dermatology'}</t>
+          <t>Dermatology</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>medical_procedure_knowledge_quiz_specialty_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option3':_'gastroenterology'}</t>
+          <t>gastroenterology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option3': 'Gastroenterology'}</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>medical_procedure_knowledge_quiz_specialty_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option4':_'nephrology'}</t>
+          <t>nephrology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option4': 'Nephrology'}</t>
+          <t>Nephrology</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>medical_procedure_knowledge_quiz_procedures_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option1':_'blood_test'}</t>
+          <t>blood_test</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option1': 'Blood test'}</t>
+          <t>Blood test</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>medical_procedure_knowledge_quiz_procedures_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option2':_'biopsy'}</t>
+          <t>biopsy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option2': 'Biopsy'}</t>
+          <t>Biopsy</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>medical_procedure_knowledge_quiz_procedures_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option3':_'mri_scan'}</t>
+          <t>mri_scan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option3': 'MRI scan'}</t>
+          <t>MRI scan</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>medical_procedure_knowledge_quiz_procedures_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option4':_'ct_scan'}</t>
+          <t>ct_scan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option4': 'CT scan'}</t>
+          <t>CT scan</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>medical_procedure_knowledge_quiz_procedures_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option5':_'x-ray'}</t>
+          <t>x-ray</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option5': 'X-ray'}</t>
+          <t>X-ray</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>medical_procedure_knowledge_quiz_procedures_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option6':_'endoscopy'}</t>
+          <t>endoscopy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option6': 'Endoscopy'}</t>
+          <t>Endoscopy</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>medical_procedure_knowledge_quiz_hospital_affiliation_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option1':_'university_of_medicine_1'}</t>
+          <t>hospital_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option1': 'University of Medicine 1'}</t>
+          <t>Hospital 1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>medical_procedure_knowledge_quiz_hospital_affiliation_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option2':_'university_of_medicine_2'}</t>
+          <t>hospital_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option2': 'University of Medicine 2'}</t>
+          <t>Hospital 2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>medical_procedure_knowledge_quiz_hospital_affiliation_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option3':_'university_of_medicine_3'}</t>
+          <t>hospital_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option3': 'University of Medicine 3'}</t>
+          <t>Hospital 3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>medical_procedure_knowledge_quiz_hospital_affiliation_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option1':_'hospital_1'}</t>
+          <t>hospital_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option1': 'Hospital 1'}</t>
+          <t>Hospital 4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>medical_procedure_knowledge_quiz_equipment_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option2':_'hospital_2'}</t>
+          <t>ultrasound_machines</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option2': 'Hospital 2'}</t>
+          <t>Ultrasound machines</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>medical_procedure_knowledge_quiz_equipment_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option3':_'hospital_3'}</t>
+          <t>ecg_machine</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option3': 'Hospital 3'}</t>
+          <t>ECG machine</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>medical_procedure_knowledge_quiz_equipment_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option4':_'hospital_4'}</t>
+          <t>blood_analyzer</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option4': 'Hospital 4'}</t>
+          <t>Blood analyzer</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>medical_procedure_knowledge_quiz_experience_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option1':_'ultrasound_machines'}</t>
+          <t>less_than_1_year</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option1': 'Ultrasound machines'}</t>
+          <t>Less than 1 year</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>medical_procedure_knowledge_quiz_experience_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option2':_'ecg_machine'}</t>
+          <t>1-5_years</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option2': 'ECG machine'}</t>
+          <t>1-5 years</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>medical_procedure_knowledge_quiz_experience_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'option3':_'blood_analyzer'}</t>
+          <t>5-10_years</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'option3': 'Blood analyzer'}</t>
+          <t>5-10 years</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>medical_procedure_knowledge_quiz_experience_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'option1':_'doctor'}</t>
+          <t>more_than_10_years</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'option1': 'Doctor'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>question_7_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'option2':_'nurse'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'option2': 'Nurse'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>question_7_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'option3':_'technician'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'option3': 'Technician'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>question_8_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'option1':_'less_than_1_year'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'option1': 'Less than 1 year'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>question_8_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'option2':_'1-5_years'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'option2': '1-5 years'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>question_8_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'option3':_'5-10_years'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'option3': '5-10 years'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>question_8_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'option4':_'more_than_10_years'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'option4': 'More than 10 years'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>question_9_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'option1':_'blood_test'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'option1': 'Blood test'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>question_9_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'option2':_'biopsy'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'option2': 'Biopsy'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>question_9_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'option3':_'mri_scan'}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'option3': 'MRI scan'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>question_9_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'option4':_'ct_scan'}</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>{'option4': 'CT scan'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>question_9_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'option5':_'x-ray'}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'option5': 'X-ray'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>question_9_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'option6':_'endoscopy'}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'option6': 'Endoscopy'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>question_15_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'option1':_'university_of_medicine_1'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'option1': 'University of Medicine 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>question_15_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'option2':_'university_of_medicine_2'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'option2': 'University of Medicine 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>question_15_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'option3':_'university_of_medicine_3'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'option3': 'University of Medicine 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>question_16_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'option1':_'hospital_1'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'option1': 'Hospital 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>question_16_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'option2':_'hospital_2'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'option2': 'Hospital 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>question_16_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'option3':_'hospital_3'}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'option3': 'Hospital 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>question_16_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'option4':_'hospital_4'}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'option4': 'Hospital 4'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>question_17_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'option1':_'ultrasound_machines'}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'option1': 'Ultrasound machines'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>question_17_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'option2':_'ecg_machine'}</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>{'option2': 'ECG machine'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>question_17_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>{'option3':_'blood_analyzer'}</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>{'option3': 'Blood analyzer'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>question_18_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>{'option1':_'doctor'}</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>{'option1': 'Doctor'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>question_18_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>{'option2':_'nurse'}</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>{'option2': 'Nurse'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>question_18_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>{'option3':_'technician'}</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>{'option3': 'Technician'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>question_19_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>{'option1':_'less_than_1_year'}</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>{'option1': 'Less than 1 year'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>question_19_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>{'option2':_'1-5_years'}</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>{'option2': '1-5 years'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>question_19_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>{'option3':_'5-10_years'}</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>{'option3': '5-10 years'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>question_19_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>{'option4':_'more_than_10_years'}</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>{'option4': 'More than 10 years'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>{'option1':_'blood_test'}</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>{'option1': 'Blood test'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>{'option2':_'biopsy'}</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>{'option2': 'Biopsy'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>{'option3':_'mri_scan'}</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>{'option3': 'MRI scan'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>{'option4':_'ct_scan'}</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>{'option4': 'CT scan'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>{'option5':_'x-ray'}</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>{'option5': 'X-ray'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>{'option6':_'endoscopy'}</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>{'option6': 'Endoscopy'}</t>
+          <t>More than 10 years</t>
         </is>
       </c>
     </row>
